--- a/data/polen_hist.xlsx
+++ b/data/polen_hist.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1215,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="C78">
-        <v>88.99</v>
+        <v>88.98999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -1732,7 +1732,7 @@
         <v>4</v>
       </c>
       <c r="C125">
-        <v>4.48</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="126">
@@ -1743,7 +1743,7 @@
         <v>5</v>
       </c>
       <c r="C126">
-        <v>67.20999999999999</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="127">
@@ -1754,7 +1754,139 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>15.02</v>
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>2025</v>
+      </c>
+      <c r="B128">
+        <v>7</v>
+      </c>
+      <c r="C128">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>2025</v>
+      </c>
+      <c r="B129">
+        <v>8</v>
+      </c>
+      <c r="C129">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>2025</v>
+      </c>
+      <c r="B130">
+        <v>9</v>
+      </c>
+      <c r="C130">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>2025</v>
+      </c>
+      <c r="B131">
+        <v>10</v>
+      </c>
+      <c r="C131">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>2025</v>
+      </c>
+      <c r="B132">
+        <v>11</v>
+      </c>
+      <c r="C132">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>2025</v>
+      </c>
+      <c r="B133">
+        <v>12</v>
+      </c>
+      <c r="C133">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>2026</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>2026</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>2026</v>
+      </c>
+      <c r="B136">
+        <v>3</v>
+      </c>
+      <c r="C136">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>2026</v>
+      </c>
+      <c r="B137">
+        <v>4</v>
+      </c>
+      <c r="C137">
+        <v>26.85</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>2026</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+      <c r="C138">
+        <v>56.55</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>2026</v>
+      </c>
+      <c r="B139">
+        <v>6</v>
+      </c>
+      <c r="C139">
+        <v>1.97</v>
       </c>
     </row>
   </sheetData>
